--- a/daily_matches/job_matches_2026-05-30.xlsx
+++ b/daily_matches/job_matches_2026-05-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote in CA)</t>
+          <t>Associate Data Solutions Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Redshift, BigQuery, Data Lake, Docker, Kubernetes, Apache Airflow, Snowflake, Databricks</t>
+          <t>Data Scientist, RAG, S3, Glue, Redshift, BigQuery, Data Lake, Kinesis, Dataflow, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=096ec33d45508f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c665018c2e31d8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote in CA)</t>
+          <t>Cloud &amp; Digital Platform DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Diality</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.3</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Redshift, BigQuery, Data Lake, Docker, Kubernetes, Apache Airflow, Snowflake, Databricks</t>
+          <t>RAG, Copilot, S3, EC2, Redshift, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88c69f0d47a40e9</t>
+          <t>https://www.indeed.com/viewjob?jk=905414e7ceb13800</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior IT App Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, LLaMA, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,19 +566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0df4b6355f101906</t>
+          <t>https://www.indeed.com/viewjob?jk=8f9b9650d1bc3a54</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ai Architect</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21.1</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, AWS SageMaker</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b842ee858dea9c</t>
+          <t>https://www.indeed.com/viewjob?jk=efb82b07adb9feba</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21.1</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Azure ML, Azure ML Studio, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd2d99f50f24a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=65195644bb1b9e0b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Java Backend Developer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54b978fe434499e3</t>
+          <t>https://www.indeed.com/viewjob?jk=75e8ade515a41a57</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Junior DevSecOps Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BLN24</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfca486d25deb1b</t>
+          <t>https://www.indeed.com/viewjob?jk=859e82cabfb17666</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, BigQuery, Dataflow, CI/CD, Jenkins, Terraform, Git, BigQuery, MySQL, SQL</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c250c7540d478f32</t>
+          <t>https://www.indeed.com/viewjob?jk=f143b13efb8ce9b6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Infrastructure</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MLflow, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks, Kafka</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bcc3fe3fd715833</t>
+          <t>https://www.indeed.com/viewjob?jk=5a031b4964c2a255</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer- Snowflake &amp; Azure</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copilot, Cortex, Kubernetes, AKS, CI/CD, Terraform, Git, Snowflake, Python, SQL</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763fd8f53ea47c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=c4349cc4f94a5d87</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aptean</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Synapse, Dataflow, CI/CD, GitHub Actions, Git, Databricks, PySpark, Power BI, Python, SQL</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef802648dc8c758d</t>
+          <t>https://www.indeed.com/viewjob?jk=e66448573f4489d1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Insight Software</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Copilot, Prompt Engineering, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Power BI, SQL, R</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f17a3a493c5baa0</t>
+          <t>https://www.indeed.com/viewjob?jk=ddbf7440ad773888</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Backend Software Engineer III – Supply Chain &amp; Operations</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=449bf406ed93070c</t>
+          <t>https://www.indeed.com/viewjob?jk=b72f3a18139b7e54</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=827fbdbb8d308839</t>
+          <t>https://www.indeed.com/viewjob?jk=7467917f2474b2e9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=465cb5a1f603f653</t>
+          <t>https://www.indeed.com/viewjob?jk=741f313dfe0a4767</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adaf4690cedeb1f1</t>
+          <t>https://www.indeed.com/viewjob?jk=fb549dda19deb4df</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rockstar Games</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, MLflow, CI/CD, Terraform, Git, Databricks, R, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b9a62cd3f890eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=ad53455736c94aa1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Quality Analyst (contract)</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, Git, Kafka, NoSQL, SQL, R, Java</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66facfd51590ff07</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf96d3e5672d2dd</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rockstar Games</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Terraform, Git, Databricks, PySpark, Python, SQL, R</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff9577ea6268d55</t>
+          <t>https://www.indeed.com/viewjob?jk=a2abd6bece93c89e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rockstar Games</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Terraform, Git, Databricks, PySpark, Python, SQL, R</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a641f1e5d1f5576</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7b4a6316115547</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Fullstack</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Docker, Kubernetes, Databricks, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e1d5edd7f6cfacc</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef2a2c6485dc8ce</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Infrastructure and Tools</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, Terraform, Databricks, Python, R, Java</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92d9bf233ed60118</t>
+          <t>https://www.indeed.com/viewjob?jk=f8777195f0640326</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, CI/CD, Snowflake, Kafka, Python, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc99c4d09fcc8c74</t>
+          <t>https://www.indeed.com/viewjob?jk=8b251c80469648dc</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Databricks, Kafka, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eba83b04e857d00</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad5e6a6c6033f66</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - GSI's and FinTech Data</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Databricks, Kafka, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44ec35e1f7566eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=4439501b54b34a7a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - AI Natives Business</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, MLflow, Git, Databricks, Kafka, Hadoop, Python, SQL, R</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d884fcaeec353d16</t>
+          <t>https://www.indeed.com/viewjob?jk=1151c815185cd79e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Financial Services (Insurance)</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Databricks, Kafka, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df17d8e1960c7150</t>
+          <t>https://www.indeed.com/viewjob?jk=d6614c39234b9da2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spokane Valley, WA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Databricks, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b11f37b58c06df</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7e23c7f438f8c8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Databricks, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e166dda8b8fb2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=e8663ead75611c2e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Gesa Credit Union</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Richland, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Databricks, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38d66edddd66e10c</t>
+          <t>https://www.indeed.com/viewjob?jk=51de78e580811e18</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer II - Commerce</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eca85f8d1685ca3</t>
+          <t>https://www.indeed.com/viewjob?jk=548feeaa37b8c916</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer II - Identity</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36c7d64e7151f3b2</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf7d70224611ecc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer (Public Cloud)</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15f135e1f3ef110</t>
+          <t>https://www.indeed.com/viewjob?jk=08e283453e85139f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID)</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>C-4 Analytics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, MongoDB, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8edb5fa1179b0b82</t>
+          <t>https://www.indeed.com/viewjob?jk=ecaa2a1fd433f4a4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Distributed Data Systems</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, MLflow, Databricks, Hadoop, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f494d2abfb9b3a</t>
+          <t>https://www.indeed.com/viewjob?jk=dd01c10e73409cc8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Distributed Data Systems</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, MLflow, Databricks, Hadoop, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35301f7890450ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=3166241cc8c62f5d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Distributed Data Systems</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, MLflow, Databricks, Hadoop, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f178ac0bdca2782a</t>
+          <t>https://www.indeed.com/viewjob?jk=1572589542133e74</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer - GTM Strategy and Operations</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a0bb155afd6ca48</t>
+          <t>https://www.indeed.com/viewjob?jk=a2ec3f9f81325aa0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b913975595a0971</t>
+          <t>https://www.indeed.com/viewjob?jk=492f0c5d5b1026f4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd5f2d847f0ba919</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5a1bf124fcc939</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211c16683969763d</t>
+          <t>https://www.indeed.com/viewjob?jk=e7780a9fb7958201</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Customer Enablement Specialist</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Data Lake, MLflow, Git, Databricks, Tableau, Power BI, SQL, R, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b3cf6067f02e47</t>
+          <t>https://www.indeed.com/viewjob?jk=fd18a128a4672b91</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer, Retail - CPG</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>MLflow, Databricks, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5f3f7a370e649b</t>
+          <t>https://www.indeed.com/viewjob?jk=ea676aaaba70e2d7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Emerging</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>MLflow, Databricks, Kafka, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7afdce6cf8faaddf</t>
+          <t>https://www.indeed.com/viewjob?jk=cab3ba747ce4a550</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>MLflow, Databricks, Kafka, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ce1a2957006a72</t>
+          <t>https://www.indeed.com/viewjob?jk=d65e39a595440fab</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Customer Enablement Specialist</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Data Lake, MLflow, Git, Databricks, Tableau, Power BI, SQL, R, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d07bf6e7b39b73b5</t>
+          <t>https://www.indeed.com/viewjob?jk=55cb9c48e2f72a54</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Fullstack</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MLflow, Docker, Kubernetes, Databricks, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d41030c2a031bc3</t>
+          <t>https://www.indeed.com/viewjob?jk=b3a01b8449781d9b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Fullstack</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MLflow, Docker, Kubernetes, Databricks, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e37bcb174213c7a</t>
+          <t>https://www.indeed.com/viewjob?jk=5fa7561c868d2097</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Docker, Kubernetes, Databricks, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,42 +2176,5012 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9446abbf0a9e21d5</t>
+          <t>https://www.indeed.com/viewjob?jk=3a729d7eaa711e20</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend</t>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f022796cfb8fbcc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7c33b5572cf45fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8762f88f61ad7223</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Cyber Forward Deployed Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=efdfb03d10f7ec00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Illumina</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1f47be0a4275bc7</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Infrastructure</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Decagon</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>San Francisco, CA, US USA</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D56" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Kubernetes, AKS, CI/CD, Terraform, Git, Snowflake, Databricks</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3d218109f5a2e7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Infrastructure</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Decagon</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Kubernetes, AKS, CI/CD, Terraform, Git, Snowflake, Databricks</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb96afd07bcd39f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Weyerhaeuser</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Glue, Data Lake, CI/CD, Terraform, Git, Snowflake, Kafka, Power BI</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=330bf279fb8cd838</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, FAISS, Pinecone, S3, CI/CD, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3ac436669ece2e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Sr. Systems Engineer- Cloud Infrastructure Engineering</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4de6e8c6244caa58</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Fabletics</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>El Segundo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, PySpark, Python</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ac7bdb141d55008</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Associate AI Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Rakuten International</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6bb2a21fd72bb8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Headspace</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Data Lake, Terraform, Snowflake, Databricks, Redshift, PySpark, Python, R</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4edb47917f0e6215</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Headspace</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Data Lake, Terraform, Snowflake, Databricks, Redshift, PySpark, Python, R</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e84f993a048191bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior Engineer II- Software Edge AI</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Microchip Technology</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Chandler, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, Keras, EC2, Data Lake, FastAPI, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19cdd2e7d1c77772</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Arlington Heights, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=660f1c31ac0ed09f</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b32bb999cb1a1bbf</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe9fca936b332884</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=682a9b15f229f11d</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Inglewood, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=135487e70d5bfaf7</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eaff9b8ecc6e96a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Honolulu, HI, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b120e904d8952628</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Fresno, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b2f68dffdd40ba5</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Westlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47005759e664e472</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2c80b6b66b80b46</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82408d4c83d37cfc</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67db148bce476e46</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a04eac4c91b0261d</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Midland, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb73841b6798442d</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=081487e3b8cc20d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=131eb379d35be9a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0251607cd5edec03</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=859b5aa7eed2396c</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=36e4241abb5acae4</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9067cb09680d0e28</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e3318c27a9db84d</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2d619df00e838cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a323dd11a8a43d58</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55201459985a6512</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55e41412c055320d</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39127f880ecb1e9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91794d7a3e8ca705</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61c3672e586f3615</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Lansing, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=160b3e9706a66d12</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59e64276b5701346</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac22f87caa73893a</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=450a545fccd00f1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3da29497726d19ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcd3f9bf937fc867</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fb89953b32bfc84</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4079ddff9773beb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de1eaa8fe73087ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=199d1c78d2743ede</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Jericho, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85d8a719f198de7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2635edbdd77391d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Williamsville, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0120459c0fbc1849</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a99a4ae145b8a71</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=741b65df42b79842</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0881ea7592c5f775</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f5cde644a1d74ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e71e6531d43812a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67e5a1ae21eb4453</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=401facedfa5c9379</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2bd2c4c1d44789aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee8f1863f7a993c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38798b58c75a2836</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8bdc456ba190ce2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=adfc818213476ba5</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=923b3050ecd9a814</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f298bcfba0ee5335</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6caad744a79fbd9</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=121ee17c011598c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3699598baf4cf831</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b1a66861ef46a96</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a9fbd6eb6aaa994</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5dc212a50769a414</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e297249d8e843a39</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=412915c30ad20fac</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Wichita, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfdffd84abdf3f2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=523d50e65e671c2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e4bee788af20c0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5616af4ce8a8a8f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97668ec4fe7745c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Rochester, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76ee94db66cb8573</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2bb3f6e0f211bef</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=272c553491b0ae44</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef9903d1c88875ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48392b680a1b3a6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0df525ebf22ff9fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=378bc22c73e9ef33</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d78966b489cfea6</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Monterey, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7df89441141527ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc42c2a4e5140f69</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66e65258ac69fefd</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7b8c309e1dd4b82</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f98038822e26dd8</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a55ba7ce9c7c4713</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85557e4da3ee4405</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4c9edfc26a261dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc933305859d57b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18e6b1969d6c7210</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7e1d701408b5626</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=288dfb7ead95495d</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fa85911435d672d</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9b1c071eb4265fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16f343db215cfb2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c44c288bccc8a6a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=211ece43a6639e15</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=117b69fc0cf106cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a31df839c27886a</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2e202fe647fc8c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c1275067df0fefc</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b046a816c53c475</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d0dcc0f31186adf</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26a73c1c18e4feb1</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c162c04d00001e41</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d72aa3d302823165</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=437542252a94a7bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1db9b5fd4ad91c79</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c338c18f5cc8b343</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b85cee4884732fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87011ec9083a8b23</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1d4cefa45bd4112</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66e3413d7b223f3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f780ced93a3bc16</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a4ad2ff105c8b83</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=430e2adbc8757712</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43daf093c3246e39</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90d2c0b1b77db71f</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db8c787399aa7569</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afd791e19de5a0fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e23b8b93066067d</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa821c9250f94164</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>AI Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f15f76b6c67bbdd</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Pager Health</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4200b4cb89b14da6</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Software Developer II - Customer Care &amp; Billing Utility Software (Front End)</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>National Information Solutions Cooperative (NISC)</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Lake Saint Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, Git, Kafka, Cassandra, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea0a6c0ab960490f</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Software Developer II - Customer Care &amp; Billing Utility Software (Front End)</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>National Information Solutions Cooperative (NISC)</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Mandan, ND, US USA</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, Git, Kafka, Cassandra, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52a5c1f9c02ef711</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Software Developer II - Customer Care &amp; Billing Utility Software (Front End)</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>National Information Solutions Cooperative (NISC)</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Cedar Rapids, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, Git, Kafka, Cassandra, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=342ed56eff6d68fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Internship, Software Engineer, AI Data Infrastructure (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
         <v>10</v>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>RAG, MLflow, Docker, Kubernetes, Databricks, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4cf9f394fc466cab</t>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Terraform, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f2c3d057b6343da</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Pittsburgh Penguins</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>10</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, BigQuery, Apache Airflow, Git, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97f84573b571ac95</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>MAGNETO &amp; DIESEL INJECTOR SERVICE</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Humble, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>10</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d19cafe12d10dcef</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Backend Software Engineer II – Supply Chain &amp; Operations</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Blue Origin</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>10</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b49e9dfb21312e82</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Production Support Engineer</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Millennium Management</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>10</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Generative AI, Jenkins, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5a6865aa45ed123</t>
         </is>
       </c>
     </row>
